--- a/media/Levels/Level_12.xlsx
+++ b/media/Levels/Level_12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B17313-4AB2-4938-A71D-349033945D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FDCDBE-0EA3-41B8-9B86-11061FD36453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="576" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -887,19 +887,7 @@
       <c r="BV2" s="1">
         <v>0</v>
       </c>
-      <c r="CU2" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV2" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW2" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX2" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY2" s="4">
+      <c r="CW2" s="1">
         <v>0</v>
       </c>
       <c r="EP2" s="1">
@@ -913,20 +901,8 @@
       <c r="BV3" s="1">
         <v>4</v>
       </c>
-      <c r="CU3" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV3" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW3" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX3" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY3" s="4">
-        <v>0</v>
+      <c r="CW3" s="1">
+        <v>4</v>
       </c>
       <c r="EQ3" s="1">
         <v>0</v>
@@ -939,19 +915,7 @@
       <c r="BV4" s="1">
         <v>0</v>
       </c>
-      <c r="CU4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW4" s="4">
-        <v>11</v>
-      </c>
-      <c r="CX4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY4" s="4">
+      <c r="CW4" s="1">
         <v>0</v>
       </c>
       <c r="ER4" s="1">
@@ -965,19 +929,7 @@
       <c r="BV5" s="1">
         <v>0</v>
       </c>
-      <c r="CU5" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV5" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW5" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX5" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY5" s="4">
+      <c r="CW5" s="1">
         <v>0</v>
       </c>
       <c r="ES5" s="1">
@@ -991,20 +943,8 @@
       <c r="BV6" s="1">
         <v>4</v>
       </c>
-      <c r="CU6" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV6" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW6" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX6" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY6" s="4">
-        <v>0</v>
+      <c r="CW6" s="1">
+        <v>4</v>
       </c>
       <c r="ET6" s="1">
         <v>0</v>
@@ -1017,19 +957,7 @@
       <c r="BV7" s="1">
         <v>0</v>
       </c>
-      <c r="CU7" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV7" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW7" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX7" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY7" s="4">
+      <c r="CW7" s="1">
         <v>0</v>
       </c>
       <c r="ET7" s="1">
@@ -1043,19 +971,7 @@
       <c r="BV8" s="1">
         <v>0</v>
       </c>
-      <c r="CU8" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV8" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW8" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX8" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY8" s="4">
+      <c r="CW8" s="1">
         <v>0</v>
       </c>
       <c r="ET8" s="1">
@@ -1069,20 +985,8 @@
       <c r="BV9" s="1">
         <v>4</v>
       </c>
-      <c r="CU9" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV9" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW9" s="4">
-        <v>11</v>
-      </c>
-      <c r="CX9" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY9" s="4">
-        <v>0</v>
+      <c r="CW9" s="1">
+        <v>4</v>
       </c>
       <c r="ET9" s="1">
         <v>0</v>
@@ -1095,19 +999,7 @@
       <c r="BV10" s="1">
         <v>0</v>
       </c>
-      <c r="CU10" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV10" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW10" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX10" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY10" s="4">
+      <c r="CW10" s="1">
         <v>0</v>
       </c>
       <c r="ET10" s="1">
@@ -1136,6 +1028,21 @@
       <c r="BV11" s="3">
         <v>0</v>
       </c>
+      <c r="CE11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH11" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI11" s="4">
+        <v>0</v>
+      </c>
       <c r="CU11" s="4">
         <v>0</v>
       </c>
@@ -1149,21 +1056,6 @@
         <v>0</v>
       </c>
       <c r="CY11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC11" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF11" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG11" s="4">
         <v>0</v>
       </c>
       <c r="ET11" s="1">
@@ -1207,9 +1099,6 @@
       <c r="BV12" s="3">
         <v>8</v>
       </c>
-      <c r="CD12" s="4">
-        <v>0</v>
-      </c>
       <c r="CE12" s="4">
         <v>0</v>
       </c>
@@ -1222,6 +1111,9 @@
       <c r="CH12" s="4">
         <v>0</v>
       </c>
+      <c r="CI12" s="4">
+        <v>0</v>
+      </c>
       <c r="CU12" s="4">
         <v>0</v>
       </c>
@@ -1235,36 +1127,6 @@
         <v>0</v>
       </c>
       <c r="CY12" s="4">
-        <v>0</v>
-      </c>
-      <c r="DN12" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO12" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP12" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ12" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR12" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC12" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED12" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE12" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF12" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG12" s="4">
         <v>0</v>
       </c>
       <c r="ET12" s="1">
@@ -1308,9 +1170,6 @@
       <c r="BV13" s="3">
         <v>0</v>
       </c>
-      <c r="CD13" s="4">
-        <v>0</v>
-      </c>
       <c r="CE13" s="4">
         <v>0</v>
       </c>
@@ -1318,11 +1177,14 @@
         <v>0</v>
       </c>
       <c r="CG13" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CH13" s="4">
         <v>0</v>
       </c>
+      <c r="CI13" s="4">
+        <v>0</v>
+      </c>
       <c r="CU13" s="4">
         <v>0</v>
       </c>
@@ -1330,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="CW13" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CX13" s="4">
         <v>0</v>
@@ -1351,21 +1213,6 @@
         <v>0</v>
       </c>
       <c r="DR13" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC13" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED13" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE13" s="4">
-        <v>11</v>
-      </c>
-      <c r="EF13" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG13" s="4">
         <v>0</v>
       </c>
       <c r="ET13" s="1">
@@ -1409,14 +1256,11 @@
       <c r="BV14" s="3">
         <v>0</v>
       </c>
-      <c r="CD14" s="4">
-        <v>0</v>
-      </c>
       <c r="CE14" s="4">
         <v>0</v>
       </c>
       <c r="CF14" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CG14" s="4">
         <v>0</v>
@@ -1424,6 +1268,9 @@
       <c r="CH14" s="4">
         <v>0</v>
       </c>
+      <c r="CI14" s="4">
+        <v>0</v>
+      </c>
       <c r="CU14" s="4">
         <v>0</v>
       </c>
@@ -1431,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="CW14" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CX14" s="4">
         <v>0</v>
@@ -1446,27 +1293,12 @@
         <v>0</v>
       </c>
       <c r="DP14" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="DQ14" s="4">
         <v>0</v>
       </c>
       <c r="DR14" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC14" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED14" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE14" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF14" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG14" s="4">
         <v>0</v>
       </c>
       <c r="ET14" s="1">
@@ -1510,9 +1342,6 @@
       <c r="BV15" s="3">
         <v>8</v>
       </c>
-      <c r="CD15" s="4">
-        <v>0</v>
-      </c>
       <c r="CE15" s="4">
         <v>0</v>
       </c>
@@ -1525,6 +1354,9 @@
       <c r="CH15" s="4">
         <v>0</v>
       </c>
+      <c r="CI15" s="4">
+        <v>0</v>
+      </c>
       <c r="CU15" s="4">
         <v>0</v>
       </c>
@@ -1547,27 +1379,12 @@
         <v>0</v>
       </c>
       <c r="DP15" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="DQ15" s="4">
         <v>0</v>
       </c>
       <c r="DR15" s="4">
-        <v>0</v>
-      </c>
-      <c r="EC15" s="4">
-        <v>0</v>
-      </c>
-      <c r="ED15" s="4">
-        <v>0</v>
-      </c>
-      <c r="EE15" s="4">
-        <v>0</v>
-      </c>
-      <c r="EF15" s="4">
-        <v>0</v>
-      </c>
-      <c r="EG15" s="4">
         <v>0</v>
       </c>
       <c r="ET15" s="1">
@@ -1596,36 +1413,6 @@
       <c r="BV16" s="3">
         <v>0</v>
       </c>
-      <c r="CD16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX16" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY16" s="4">
-        <v>0</v>
-      </c>
       <c r="DN16" s="4">
         <v>0</v>
       </c>
@@ -1678,19 +1465,7 @@
       <c r="BV18" s="1">
         <v>4</v>
       </c>
-      <c r="DN18" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO18" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP18" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ18" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR18" s="4">
+      <c r="DP18" s="1">
         <v>0</v>
       </c>
       <c r="ET18" s="1">
@@ -1704,20 +1479,8 @@
       <c r="BV19" s="1">
         <v>0</v>
       </c>
-      <c r="DN19" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO19" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP19" s="4">
-        <v>11</v>
-      </c>
-      <c r="DQ19" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR19" s="4">
-        <v>0</v>
+      <c r="DP19" s="1">
+        <v>4</v>
       </c>
       <c r="ET19" s="1">
         <v>0</v>
@@ -1790,19 +1553,7 @@
       <c r="BV20" s="1">
         <v>0</v>
       </c>
-      <c r="DN20" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO20" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP20" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ20" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR20" s="4">
+      <c r="DP20" s="1">
         <v>0</v>
       </c>
       <c r="ET20" s="1">
@@ -1876,34 +1627,7 @@
       <c r="BV21" s="1">
         <v>4</v>
       </c>
-      <c r="DN21" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO21" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP21" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ21" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR21" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO21" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP21" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ21" s="4">
-        <v>0</v>
-      </c>
-      <c r="ER21" s="4">
-        <v>0</v>
-      </c>
-      <c r="ES21" s="4">
+      <c r="DP21" s="1">
         <v>0</v>
       </c>
       <c r="ET21" s="1">
@@ -1977,35 +1701,8 @@
       <c r="BV22" s="1">
         <v>0</v>
       </c>
-      <c r="DN22" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO22" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP22" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ22" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR22" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO22" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP22" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ22" s="4">
-        <v>0</v>
-      </c>
-      <c r="ER22" s="4">
-        <v>0</v>
-      </c>
-      <c r="ES22" s="4">
-        <v>0</v>
+      <c r="DP22" s="1">
+        <v>4</v>
       </c>
       <c r="ET22" s="1">
         <v>0</v>
@@ -2078,34 +1775,7 @@
       <c r="BV23" s="1">
         <v>0</v>
       </c>
-      <c r="DN23" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO23" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP23" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ23" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR23" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO23" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP23" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ23" s="4">
-        <v>11</v>
-      </c>
-      <c r="ER23" s="4">
-        <v>0</v>
-      </c>
-      <c r="ES23" s="4">
+      <c r="DP23" s="1">
         <v>0</v>
       </c>
       <c r="ET23" s="1">
@@ -2179,34 +1849,7 @@
       <c r="BV24" s="1">
         <v>4</v>
       </c>
-      <c r="DN24" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO24" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP24" s="4">
-        <v>11</v>
-      </c>
-      <c r="DQ24" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR24" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO24" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP24" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ24" s="4">
-        <v>0</v>
-      </c>
-      <c r="ER24" s="4">
-        <v>0</v>
-      </c>
-      <c r="ES24" s="4">
+      <c r="DP24" s="1">
         <v>0</v>
       </c>
       <c r="ET24" s="1">
@@ -2280,35 +1923,8 @@
       <c r="BV25" s="1">
         <v>0</v>
       </c>
-      <c r="DN25" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO25" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP25" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ25" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR25" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO25" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP25" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ25" s="4">
-        <v>0</v>
-      </c>
-      <c r="ER25" s="4">
-        <v>0</v>
-      </c>
-      <c r="ES25" s="4">
-        <v>0</v>
+      <c r="DP25" s="1">
+        <v>4</v>
       </c>
       <c r="ET25" s="1">
         <v>0</v>
@@ -2381,19 +1997,7 @@
       <c r="BV26" s="1">
         <v>0</v>
       </c>
-      <c r="DN26" s="4">
-        <v>0</v>
-      </c>
-      <c r="DO26" s="4">
-        <v>0</v>
-      </c>
-      <c r="DP26" s="4">
-        <v>0</v>
-      </c>
-      <c r="DQ26" s="4">
-        <v>0</v>
-      </c>
-      <c r="DR26" s="4">
+      <c r="DP26" s="1">
         <v>0</v>
       </c>
       <c r="ET26" s="1">
@@ -5833,6 +5437,21 @@
       <c r="DX69" s="1">
         <v>0</v>
       </c>
+      <c r="EH69" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI69" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ69" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK69" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL69" s="4">
+        <v>0</v>
+      </c>
       <c r="ET69" s="1">
         <v>0</v>
       </c>
@@ -5970,6 +5589,21 @@
       <c r="DX70" s="1">
         <v>0</v>
       </c>
+      <c r="EH70" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI70" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ70" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK70" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL70" s="4">
+        <v>0</v>
+      </c>
       <c r="ET70" s="1">
         <v>0</v>
       </c>
@@ -6107,6 +5741,21 @@
       <c r="DX71" s="1">
         <v>4</v>
       </c>
+      <c r="EH71" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI71" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ71" s="4">
+        <v>11</v>
+      </c>
+      <c r="EK71" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL71" s="4">
+        <v>0</v>
+      </c>
       <c r="ET71" s="1">
         <v>0</v>
       </c>
@@ -6244,6 +5893,21 @@
       <c r="DX72" s="1">
         <v>0</v>
       </c>
+      <c r="EH72" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI72" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ72" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK72" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL72" s="4">
+        <v>0</v>
+      </c>
       <c r="ET72" s="1">
         <v>0</v>
       </c>
@@ -6394,6 +6058,21 @@
         <v>0</v>
       </c>
       <c r="DX73" s="1">
+        <v>0</v>
+      </c>
+      <c r="EH73" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI73" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ73" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK73" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL73" s="4">
         <v>0</v>
       </c>
       <c r="ET73" s="1">
@@ -6773,6 +6452,21 @@
       <c r="A77" s="1">
         <v>0</v>
       </c>
+      <c r="I77" s="4">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0</v>
+      </c>
+      <c r="K77" s="4">
+        <v>0</v>
+      </c>
+      <c r="L77" s="4">
+        <v>0</v>
+      </c>
+      <c r="M77" s="4">
+        <v>0</v>
+      </c>
       <c r="U77" s="1">
         <v>4</v>
       </c>
@@ -6868,6 +6562,21 @@
       <c r="A78" s="1">
         <v>0</v>
       </c>
+      <c r="I78" s="4">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0</v>
+      </c>
+      <c r="K78" s="4">
+        <v>0</v>
+      </c>
+      <c r="L78" s="4">
+        <v>0</v>
+      </c>
+      <c r="M78" s="4">
+        <v>0</v>
+      </c>
       <c r="U78" s="1">
         <v>0</v>
       </c>
@@ -6948,6 +6657,21 @@
       <c r="A79" s="1">
         <v>0</v>
       </c>
+      <c r="I79" s="4">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4">
+        <v>11</v>
+      </c>
+      <c r="L79" s="4">
+        <v>0</v>
+      </c>
+      <c r="M79" s="4">
+        <v>0</v>
+      </c>
       <c r="U79" s="1">
         <v>0</v>
       </c>
@@ -7028,6 +6752,21 @@
       <c r="A80" s="1">
         <v>0</v>
       </c>
+      <c r="I80" s="4">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4">
+        <v>0</v>
+      </c>
+      <c r="K80" s="4">
+        <v>0</v>
+      </c>
+      <c r="L80" s="4">
+        <v>0</v>
+      </c>
+      <c r="M80" s="4">
+        <v>0</v>
+      </c>
       <c r="U80" s="1">
         <v>4</v>
       </c>
@@ -7108,6 +6847,21 @@
       <c r="A81" s="1">
         <v>0</v>
       </c>
+      <c r="I81" s="4">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4">
+        <v>0</v>
+      </c>
+      <c r="L81" s="4">
+        <v>0</v>
+      </c>
+      <c r="M81" s="4">
+        <v>0</v>
+      </c>
       <c r="U81" s="1">
         <v>0</v>
       </c>
@@ -7704,21 +7458,6 @@
       <c r="EH88" s="4">
         <v>0</v>
       </c>
-      <c r="EL88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP88" s="4">
-        <v>0</v>
-      </c>
       <c r="ET88" s="1">
         <v>0</v>
       </c>
@@ -7841,21 +7580,6 @@
       <c r="EH89" s="4">
         <v>0</v>
       </c>
-      <c r="EL89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP89" s="4">
-        <v>0</v>
-      </c>
       <c r="ET89" s="1">
         <v>0</v>
       </c>
@@ -8041,30 +7765,6 @@
       <c r="EH90" s="4">
         <v>0</v>
       </c>
-      <c r="EL90" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM90" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN90" s="4">
-        <v>11</v>
-      </c>
-      <c r="EO90" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP90" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ90" s="1">
-        <v>0</v>
-      </c>
-      <c r="ER90" s="1">
-        <v>3</v>
-      </c>
-      <c r="ES90" s="1">
-        <v>0</v>
-      </c>
       <c r="ET90" s="1">
         <v>0</v>
       </c>
@@ -8187,21 +7887,6 @@
       <c r="EH91" s="4">
         <v>0</v>
       </c>
-      <c r="EL91" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM91" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN91" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO91" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP91" s="4">
-        <v>0</v>
-      </c>
       <c r="ET91" s="1">
         <v>0</v>
       </c>
@@ -8324,21 +8009,6 @@
       <c r="EH92" s="4">
         <v>0</v>
       </c>
-      <c r="EL92" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM92" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN92" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO92" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP92" s="4">
-        <v>0</v>
-      </c>
       <c r="ET92" s="1">
         <v>0</v>
       </c>
@@ -8749,21 +8419,6 @@
       <c r="EH102" s="4">
         <v>0</v>
       </c>
-      <c r="EL102" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM102" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN102" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO102" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP102" s="4">
-        <v>0</v>
-      </c>
       <c r="ET102" s="1">
         <v>0</v>
       </c>
@@ -8970,21 +8625,6 @@
       <c r="EH103" s="4">
         <v>0</v>
       </c>
-      <c r="EL103" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM103" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN103" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO103" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP103" s="4">
-        <v>0</v>
-      </c>
       <c r="ET103" s="1">
         <v>0</v>
       </c>
@@ -9290,30 +8930,6 @@
       <c r="EH104" s="4">
         <v>0</v>
       </c>
-      <c r="EL104" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM104" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN104" s="4">
-        <v>11</v>
-      </c>
-      <c r="EO104" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP104" s="4">
-        <v>0</v>
-      </c>
-      <c r="EQ104" s="1">
-        <v>0</v>
-      </c>
-      <c r="ER104" s="1">
-        <v>3</v>
-      </c>
-      <c r="ES104" s="1">
-        <v>0</v>
-      </c>
       <c r="ET104" s="1">
         <v>0</v>
       </c>
@@ -9520,21 +9136,6 @@
       <c r="EH105" s="4">
         <v>0</v>
       </c>
-      <c r="EL105" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM105" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN105" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO105" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP105" s="4">
-        <v>0</v>
-      </c>
       <c r="ET105" s="1">
         <v>0</v>
       </c>
@@ -9738,21 +9339,6 @@
       <c r="EH106" s="4">
         <v>0</v>
       </c>
-      <c r="EL106" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM106" s="4">
-        <v>0</v>
-      </c>
-      <c r="EN106" s="4">
-        <v>0</v>
-      </c>
-      <c r="EO106" s="4">
-        <v>0</v>
-      </c>
-      <c r="EP106" s="4">
-        <v>0</v>
-      </c>
       <c r="ET106" s="1">
         <v>0</v>
       </c>
@@ -10751,9 +10337,6 @@
       <c r="U128" s="1">
         <v>4</v>
       </c>
-      <c r="AK128" s="1">
-        <v>0</v>
-      </c>
       <c r="BO128" s="1">
         <v>0</v>
       </c>
@@ -10810,9 +10393,6 @@
       <c r="U129" s="1">
         <v>0</v>
       </c>
-      <c r="AK129" s="1">
-        <v>4</v>
-      </c>
       <c r="BO129" s="1">
         <v>0</v>
       </c>
@@ -10867,9 +10447,6 @@
         <v>0</v>
       </c>
       <c r="U130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK130" s="1">
         <v>0</v>
       </c>
       <c r="BO130" s="1">

--- a/media/Levels/Level_12.xlsx
+++ b/media/Levels/Level_12.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B17313-4AB2-4938-A71D-349033945D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{433898D4-5626-4409-ACF4-3CD296D53596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_12" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -54,7 +54,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -85,6 +85,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -100,7 +106,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -114,6 +120,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,6 +466,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938F4841-FA60-445C-98FC-D892E3E9FAF9}">
   <dimension ref="A1:ET150"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="150" max="150" width="8.796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:150" x14ac:dyDescent="0.45">
       <c r="F1" s="1">
@@ -911,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="BV3" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CU3" s="4">
         <v>0</v>
@@ -989,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="BV6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CU6" s="4">
         <v>0</v>
@@ -1067,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="BV9" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CU9" s="4">
         <v>0</v>
@@ -1204,8 +1216,8 @@
       <c r="BM12" s="4">
         <v>0</v>
       </c>
-      <c r="BV12" s="3">
-        <v>8</v>
+      <c r="BV12" s="5">
+        <v>6</v>
       </c>
       <c r="CD12" s="4">
         <v>0</v>
@@ -1507,8 +1519,8 @@
       <c r="BM15" s="4">
         <v>0</v>
       </c>
-      <c r="BV15" s="3">
-        <v>8</v>
+      <c r="BV15" s="5">
+        <v>6</v>
       </c>
       <c r="CD15" s="4">
         <v>0</v>
@@ -1676,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="BV18" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DN18" s="4">
         <v>0</v>
@@ -1874,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="BV21" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DN21" s="4">
         <v>0</v>
@@ -2177,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="BV24" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DN24" s="4">
         <v>0</v>
@@ -2468,13 +2480,13 @@
         <v>0</v>
       </c>
       <c r="BV27" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL27" s="1">
         <v>0</v>
       </c>
       <c r="CM27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN27" s="1">
         <v>0</v>
@@ -2483,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="CP27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CQ27" s="1">
         <v>0</v>
@@ -2492,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="CS27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CT27" s="1">
         <v>0</v>
@@ -2501,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="CV27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CW27" s="1">
         <v>0</v>
@@ -2510,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="CY27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CZ27" s="1">
         <v>0</v>
@@ -2519,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="DB27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DC27" s="1">
         <v>0</v>
@@ -2528,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="DE27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DF27" s="1">
         <v>0</v>
@@ -2537,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="DH27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DI27" s="1">
         <v>0</v>
@@ -2546,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="DK27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DL27" s="1">
         <v>0</v>
@@ -2555,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="DN27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DO27" s="1">
         <v>0</v>
@@ -2564,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="DQ27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DR27" s="1">
         <v>0</v>
@@ -2573,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="DT27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DU27" s="1">
         <v>0</v>
@@ -2582,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="DW27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DX27" s="1">
         <v>0</v>
@@ -2656,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="BD28" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV28" s="1">
         <v>0</v>
@@ -2739,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AV29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW29" s="1">
         <v>0</v>
@@ -2748,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="AY29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ29" s="1">
         <v>0</v>
@@ -2757,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="BB29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC29" s="1">
         <v>0</v>
@@ -2769,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="BF29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BG29" s="1">
         <v>0</v>
@@ -2778,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ29" s="1">
         <v>0</v>
@@ -2787,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="BL29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM29" s="1">
         <v>0</v>
@@ -2796,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="BO29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP29" s="1">
         <v>0</v>
@@ -2805,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="BR29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS29" s="1">
         <v>0</v>
@@ -2814,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="BU29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BV29" s="1">
         <v>0</v>
@@ -2823,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="BX29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BY29" s="1">
         <v>0</v>
@@ -2832,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="CA29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CB29" s="1">
         <v>0</v>
@@ -2841,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="CD29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CE29" s="1">
         <v>0</v>
@@ -2850,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="CG29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CH29" s="1">
         <v>0</v>
@@ -2859,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="CJ29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CK29" s="1">
         <v>0</v>
       </c>
       <c r="CL29" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX29" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET29" s="1">
         <v>0</v>
@@ -3016,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="BD31" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL31" s="1">
         <v>0</v>
@@ -3096,10 +3108,10 @@
         <v>0</v>
       </c>
       <c r="CL32" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX32" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET32" s="1">
         <v>0</v>
@@ -3247,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="BD34" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL34" s="1">
         <v>0</v>
@@ -3327,10 +3339,10 @@
         <v>0</v>
       </c>
       <c r="CL35" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX35" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET35" s="1">
         <v>0</v>
@@ -3508,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="BD37" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL37" s="1">
         <v>0</v>
@@ -3603,10 +3615,10 @@
         <v>0</v>
       </c>
       <c r="CL38" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX38" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET38" s="1">
         <v>0</v>
@@ -3724,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL40" s="1">
         <v>0</v>
@@ -3744,10 +3756,10 @@
         <v>0</v>
       </c>
       <c r="CL41" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX41" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET41" s="1">
         <v>0</v>
@@ -3774,8 +3786,8 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
-      <c r="BD43" s="3">
-        <v>8</v>
+      <c r="BD43" s="5">
+        <v>6</v>
       </c>
       <c r="CL43" s="1">
         <v>0</v>
@@ -3795,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="CL44" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX44" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET44" s="1">
         <v>0</v>
@@ -3825,8 +3837,8 @@
       <c r="A46" s="1">
         <v>0</v>
       </c>
-      <c r="BD46" s="3">
-        <v>8</v>
+      <c r="BD46" s="5">
+        <v>6</v>
       </c>
       <c r="CL46" s="1">
         <v>0</v>
@@ -3846,10 +3858,10 @@
         <v>0</v>
       </c>
       <c r="CL47" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX47" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET47" s="1">
         <v>0</v>
@@ -3877,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="BD49" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL49" s="1">
         <v>0</v>
@@ -3897,10 +3909,10 @@
         <v>0</v>
       </c>
       <c r="CL50" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX50" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET50" s="1">
         <v>0</v>
@@ -3928,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL52" s="1">
         <v>0</v>
@@ -3948,10 +3960,10 @@
         <v>0</v>
       </c>
       <c r="CL53" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX53" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET53" s="1">
         <v>0</v>
@@ -4129,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="BD55" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL55" s="1">
         <v>0</v>
@@ -4224,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -4233,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -4242,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" s="1">
         <v>0</v>
@@ -4251,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -4260,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U56" s="1">
         <v>0</v>
@@ -4284,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="AB56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC56" s="1">
         <v>0</v>
@@ -4293,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AE56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF56" s="1">
         <v>0</v>
@@ -4302,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="AH56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI56" s="1">
         <v>0</v>
@@ -4311,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL56" s="1">
         <v>0</v>
@@ -4320,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="AN56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO56" s="1">
         <v>0</v>
@@ -4329,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="AQ56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR56" s="1">
         <v>0</v>
@@ -4338,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="AT56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU56" s="1">
         <v>0</v>
@@ -4347,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="AW56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX56" s="1">
         <v>0</v>
@@ -4371,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="CL56" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CU56" s="2">
         <v>0</v>
@@ -4434,13 +4446,13 @@
         <v>0</v>
       </c>
       <c r="DX56" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DY56" s="1">
         <v>0</v>
       </c>
       <c r="DZ56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EA56" s="1">
         <v>0</v>
@@ -4449,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="EC56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="ED56" s="1">
         <v>0</v>
@@ -4458,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="EF56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EG56" s="1">
         <v>0</v>
@@ -4467,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="EI56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EJ56" s="1">
         <v>0</v>
@@ -4476,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="EL56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EM56" s="1">
         <v>0</v>
@@ -4485,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="EO56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EP56" s="1">
         <v>0</v>
@@ -4494,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="ER56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="ES56" s="1">
         <v>0</v>
@@ -4675,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL58" s="3">
         <v>0</v>
@@ -4754,8 +4766,8 @@
       <c r="BD59" s="1">
         <v>0</v>
       </c>
-      <c r="CL59" s="3">
-        <v>8</v>
+      <c r="CL59" s="5">
+        <v>6</v>
       </c>
       <c r="CU59" s="2">
         <v>0</v>
@@ -4818,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="DX59" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET59" s="1">
         <v>0</v>
@@ -4906,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="BD61" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL61" s="3">
         <v>0</v>
@@ -4985,8 +4997,8 @@
       <c r="BD62" s="1">
         <v>0</v>
       </c>
-      <c r="CL62" s="3">
-        <v>8</v>
+      <c r="CL62" s="5">
+        <v>6</v>
       </c>
       <c r="CU62" s="2">
         <v>0</v>
@@ -5049,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="DX62" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET62" s="1">
         <v>0</v>
@@ -5136,8 +5148,8 @@
       <c r="A64" s="1">
         <v>0</v>
       </c>
-      <c r="BD64" s="3">
-        <v>8</v>
+      <c r="BD64" s="5">
+        <v>6</v>
       </c>
       <c r="CL64" s="3">
         <v>0</v>
@@ -5216,8 +5228,8 @@
       <c r="BD65" s="3">
         <v>0</v>
       </c>
-      <c r="CL65" s="3">
-        <v>8</v>
+      <c r="CL65" s="5">
+        <v>6</v>
       </c>
       <c r="CU65" s="2">
         <v>0</v>
@@ -5280,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="DX65" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET65" s="1">
         <v>0</v>
@@ -5427,8 +5439,8 @@
       <c r="A67" s="1">
         <v>0</v>
       </c>
-      <c r="BD67" s="3">
-        <v>8</v>
+      <c r="BD67" s="5">
+        <v>6</v>
       </c>
       <c r="BM67" s="2">
         <v>0</v>
@@ -5628,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="CL68" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CM68">
         <v>0</v>
@@ -5694,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="DX68" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET68" s="1">
         <v>0</v>
@@ -5842,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="BD70" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM70" s="2">
         <v>0</v>
@@ -6042,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="CL71" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CU71" s="2">
         <v>0</v>
@@ -6105,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="DX71" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET71" s="1">
         <v>0</v>
@@ -6268,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="BD73" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM73" s="2">
         <v>0</v>
@@ -6483,10 +6495,10 @@
         <v>0</v>
       </c>
       <c r="CL74" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX74" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET74" s="1">
         <v>0</v>
@@ -6500,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W75" s="1">
         <v>0</v>
@@ -6509,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="Y75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z75" s="1">
         <v>0</v>
@@ -6518,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="AB75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC75" s="1">
         <v>0</v>
@@ -6527,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="AE75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF75" s="1">
         <v>0</v>
@@ -6536,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="AH75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI75" s="1">
         <v>0</v>
@@ -6545,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL75" s="1">
         <v>0</v>
@@ -6554,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="AN75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO75" s="1">
         <v>0</v>
@@ -6563,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="AQ75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR75" s="1">
         <v>0</v>
@@ -6572,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="AT75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU75" s="1">
         <v>0</v>
@@ -6581,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="AW75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX75" s="1">
         <v>0</v>
@@ -6697,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="BD76" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM76" s="2">
         <v>0</v>
@@ -6774,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY77" s="4">
         <v>0</v>
@@ -6855,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="CL77" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX77" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET77" s="1">
         <v>0</v>
@@ -6952,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="BD79" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM79" s="2">
         <v>0</v>
@@ -7029,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD80" s="1">
         <v>0</v>
@@ -7095,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="CL80" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX80" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET80" s="1">
         <v>0</v>
@@ -7192,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="BD82" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM82" s="2">
         <v>0</v>
@@ -7269,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD83" s="1">
         <v>0</v>
@@ -7335,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="CL83" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX83" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET83" s="1">
         <v>0</v>
@@ -7431,8 +7443,8 @@
       <c r="U85" s="1">
         <v>0</v>
       </c>
-      <c r="BD85" s="3">
-        <v>8</v>
+      <c r="BD85" s="5">
+        <v>6</v>
       </c>
       <c r="BM85" s="2">
         <v>0</v>
@@ -7509,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="U86" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK86" s="1">
         <v>0</v>
       </c>
       <c r="AL86" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM86" s="1">
         <v>0</v>
@@ -7524,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="AO86" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP86" s="1">
         <v>0</v>
@@ -7533,7 +7545,7 @@
         <v>0</v>
       </c>
       <c r="AR86" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS86" s="1">
         <v>0</v>
@@ -7542,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV86" s="1">
         <v>0</v>
@@ -7551,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="CL86" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DX86" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET86" s="1">
         <v>0</v>
@@ -7606,13 +7618,13 @@
         <v>0</v>
       </c>
       <c r="AK88" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV88" s="1">
-        <v>4</v>
-      </c>
-      <c r="BD88" s="3">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="BD88" s="5">
+        <v>6</v>
       </c>
       <c r="CJ88" s="4">
         <v>0</v>
@@ -7907,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="CP90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CQ90" s="1">
         <v>0</v>
@@ -7916,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="CS90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CT90" s="1">
         <v>0</v>
@@ -7925,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="CV90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CW90" s="1">
         <v>0</v>
@@ -7949,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="DD90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DE90" s="1">
         <v>0</v>
@@ -7973,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="DL90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DM90" s="1">
         <v>0</v>
@@ -7997,7 +8009,7 @@
         <v>0</v>
       </c>
       <c r="DT90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DU90" s="1">
         <v>0</v>
@@ -8021,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="EB90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EC90" s="1">
         <v>0</v>
@@ -8060,7 +8072,7 @@
         <v>0</v>
       </c>
       <c r="ER90" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="ES90" s="1">
         <v>0</v>
@@ -8089,13 +8101,13 @@
         <v>0</v>
       </c>
       <c r="AK91" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV91" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD91" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CJ91" s="4">
         <v>0</v>
@@ -8371,19 +8383,19 @@
         <v>0</v>
       </c>
       <c r="U94" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK94" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV94" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD94" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL94" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET94" s="1">
         <v>0</v>
@@ -8440,19 +8452,19 @@
         <v>0</v>
       </c>
       <c r="U97" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK97" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV97" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD97" s="1">
-        <v>4</v>
-      </c>
-      <c r="CL97" s="3">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="CL97" s="5">
+        <v>6</v>
       </c>
       <c r="ET97" s="1">
         <v>0</v>
@@ -8509,19 +8521,19 @@
         <v>0</v>
       </c>
       <c r="U100" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK100" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV100" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD100" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL100" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET100" s="1">
         <v>0</v>
@@ -8994,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="B104" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C104" s="4">
         <v>0</v>
@@ -9030,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="Q104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R104" s="1">
         <v>0</v>
@@ -9054,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="Y104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z104" s="1">
         <v>0</v>
@@ -9078,7 +9090,7 @@
         <v>0</v>
       </c>
       <c r="AG104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH104" s="1">
         <v>0</v>
@@ -9117,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="AZ104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA104" s="1">
         <v>0</v>
@@ -9156,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="CP104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CQ104" s="1">
         <v>0</v>
@@ -9165,7 +9177,7 @@
         <v>0</v>
       </c>
       <c r="CS104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CT104" s="1">
         <v>0</v>
@@ -9174,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="CV104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CW104" s="1">
         <v>0</v>
@@ -9198,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="DD104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DE104" s="1">
         <v>0</v>
@@ -9222,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="DL104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DM104" s="1">
         <v>0</v>
@@ -9246,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="DT104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DU104" s="1">
         <v>0</v>
@@ -9270,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="EB104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="EC104" s="1">
         <v>0</v>
@@ -9309,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="ER104" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="ES104" s="1">
         <v>0</v>
@@ -9785,10 +9797,10 @@
         <v>0</v>
       </c>
       <c r="U108" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK108" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD108" s="1">
         <v>0</v>
@@ -9797,7 +9809,7 @@
         <v>0</v>
       </c>
       <c r="EF108" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET108" s="1">
         <v>0</v>
@@ -9814,10 +9826,10 @@
         <v>0</v>
       </c>
       <c r="BD109" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL109" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF109" s="1">
         <v>0</v>
@@ -9854,10 +9866,10 @@
         <v>0</v>
       </c>
       <c r="U111" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK111" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD111" s="3">
         <v>0</v>
@@ -9866,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="EF111" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET111" s="1">
         <v>0</v>
@@ -9882,11 +9894,11 @@
       <c r="AK112" s="1">
         <v>0</v>
       </c>
-      <c r="BD112" s="3">
-        <v>8</v>
-      </c>
-      <c r="CL112" s="3">
-        <v>8</v>
+      <c r="BD112" s="5">
+        <v>6</v>
+      </c>
+      <c r="CL112" s="5">
+        <v>6</v>
       </c>
       <c r="EF112" s="1">
         <v>0</v>
@@ -9923,10 +9935,10 @@
         <v>0</v>
       </c>
       <c r="U114" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK114" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD114" s="1">
         <v>0</v>
@@ -9935,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="EF114" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET114" s="1">
         <v>0</v>
@@ -9952,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="BD115" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL115" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF115" s="1">
         <v>0</v>
@@ -9990,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="AM116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN116" s="1">
         <v>0</v>
@@ -9999,7 +10011,7 @@
         <v>0</v>
       </c>
       <c r="AP116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ116" s="1">
         <v>0</v>
@@ -10008,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="AS116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT116" s="1">
         <v>0</v>
@@ -10017,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="AV116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW116" s="1">
         <v>0</v>
@@ -10026,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="AY116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ116" s="1">
         <v>0</v>
@@ -10035,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="BB116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC116" s="1">
         <v>0</v>
@@ -10044,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="BE116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BF116" s="1">
         <v>0</v>
@@ -10056,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ116" s="1">
         <v>0</v>
@@ -10064,8 +10076,8 @@
       <c r="BK116" s="3">
         <v>0</v>
       </c>
-      <c r="BL116" s="3">
-        <v>7</v>
+      <c r="BL116" s="5">
+        <v>5</v>
       </c>
       <c r="BM116" s="3">
         <v>0</v>
@@ -10074,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="BO116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP116" s="1">
         <v>0</v>
@@ -10082,8 +10094,8 @@
       <c r="BQ116" s="3">
         <v>0</v>
       </c>
-      <c r="BR116" s="3">
-        <v>7</v>
+      <c r="BR116" s="5">
+        <v>5</v>
       </c>
       <c r="BS116" s="3">
         <v>0</v>
@@ -10092,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="BU116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BV116" s="1">
         <v>0</v>
@@ -10101,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="BX116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BY116" s="1">
         <v>0</v>
@@ -10109,8 +10121,8 @@
       <c r="BZ116" s="3">
         <v>0</v>
       </c>
-      <c r="CA116" s="3">
-        <v>7</v>
+      <c r="CA116" s="5">
+        <v>5</v>
       </c>
       <c r="CB116" s="3">
         <v>0</v>
@@ -10119,7 +10131,7 @@
         <v>0</v>
       </c>
       <c r="CD116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CE116" s="1">
         <v>0</v>
@@ -10127,8 +10139,8 @@
       <c r="CF116" s="3">
         <v>0</v>
       </c>
-      <c r="CG116" s="3">
-        <v>7</v>
+      <c r="CG116" s="5">
+        <v>5</v>
       </c>
       <c r="CH116" s="3">
         <v>0</v>
@@ -10137,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="CJ116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CK116" s="1">
         <v>0</v>
@@ -10149,7 +10161,7 @@
         <v>0</v>
       </c>
       <c r="CN116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CO116" s="1">
         <v>0</v>
@@ -10158,7 +10170,7 @@
         <v>0</v>
       </c>
       <c r="CQ116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CR116" s="1">
         <v>0</v>
@@ -10167,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="CT116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CU116" s="1">
         <v>0</v>
@@ -10176,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="CW116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CX116" s="1">
         <v>0</v>
@@ -10185,7 +10197,7 @@
         <v>0</v>
       </c>
       <c r="CZ116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DA116" s="1">
         <v>0</v>
@@ -10194,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="DC116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DD116" s="1">
         <v>0</v>
@@ -10203,7 +10215,7 @@
         <v>0</v>
       </c>
       <c r="DF116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DG116" s="1">
         <v>0</v>
@@ -10212,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="DI116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DJ116" s="1">
         <v>0</v>
@@ -10221,7 +10233,7 @@
         <v>0</v>
       </c>
       <c r="DL116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DM116" s="1">
         <v>0</v>
@@ -10230,7 +10242,7 @@
         <v>0</v>
       </c>
       <c r="DO116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DP116" s="1">
         <v>0</v>
@@ -10239,7 +10251,7 @@
         <v>0</v>
       </c>
       <c r="DR116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DS116" s="1">
         <v>0</v>
@@ -10248,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="DU116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DV116" s="1">
         <v>0</v>
@@ -10292,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO117" s="1">
         <v>0</v>
@@ -10348,16 +10360,16 @@
         <v>0</v>
       </c>
       <c r="BO118" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV118" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD118" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV118" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ED118" s="4">
         <v>0</v>
@@ -10451,7 +10463,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO120" s="1">
         <v>0</v>
@@ -10495,16 +10507,16 @@
         <v>0</v>
       </c>
       <c r="BO121" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV121" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD121" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV121" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF121" s="1">
         <v>0</v>
@@ -10518,7 +10530,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO122" s="1">
         <v>0</v>
@@ -10533,7 +10545,7 @@
         <v>0</v>
       </c>
       <c r="EF122" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET122" s="1">
         <v>0</v>
@@ -10573,16 +10585,16 @@
         <v>0</v>
       </c>
       <c r="BO124" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV124" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD124" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV124" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF124" s="1">
         <v>0</v>
@@ -10596,7 +10608,7 @@
         <v>0</v>
       </c>
       <c r="U125" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO125" s="1">
         <v>0</v>
@@ -10611,7 +10623,7 @@
         <v>0</v>
       </c>
       <c r="EF125" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET125" s="1">
         <v>0</v>
@@ -10696,13 +10708,13 @@
         <v>0</v>
       </c>
       <c r="BO127" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV127" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD127" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DK127" s="4">
         <v>0</v>
@@ -10720,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="DV127" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF127" s="1">
         <v>0</v>
@@ -10749,7 +10761,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK128" s="1">
         <v>0</v>
@@ -10782,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="EF128" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET128" s="1">
         <v>0</v>
@@ -10811,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO129" s="1">
         <v>0</v>
@@ -10873,13 +10885,13 @@
         <v>0</v>
       </c>
       <c r="BO130" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV130" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD130" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DK130" s="4">
         <v>0</v>
@@ -10897,7 +10909,7 @@
         <v>0</v>
       </c>
       <c r="DV130" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF130" s="1">
         <v>0</v>
@@ -10911,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK131" s="1">
         <v>0</v>
@@ -10929,7 +10941,7 @@
         <v>0</v>
       </c>
       <c r="EF131" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET131" s="1">
         <v>0</v>
@@ -10943,7 +10955,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO132" s="1">
         <v>0</v>
@@ -10975,16 +10987,16 @@
         <v>0</v>
       </c>
       <c r="BO133" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV133" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD133" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV133" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ED133" s="4">
         <v>0</v>
@@ -11010,7 +11022,7 @@
         <v>0</v>
       </c>
       <c r="U134" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK134" s="1">
         <v>0</v>
@@ -11054,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="AK135" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO135" s="1">
         <v>0</v>
@@ -11125,13 +11137,13 @@
         <v>0</v>
       </c>
       <c r="BO136" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV136" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD136" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CW136" s="4">
         <v>0</v>
@@ -11149,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="DV136" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ED136" s="4">
         <v>0</v>
@@ -11258,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="AK138" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO138" s="1">
         <v>0</v>
@@ -11317,13 +11329,13 @@
         <v>0</v>
       </c>
       <c r="BO139" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV139" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD139" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CW139" s="4">
         <v>0</v>
@@ -11341,10 +11353,10 @@
         <v>0</v>
       </c>
       <c r="DV139" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF139" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET139" s="1">
         <v>0</v>
@@ -11373,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="AL140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM140" s="1">
         <v>0</v>
@@ -11382,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="AO140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP140" s="1">
         <v>0</v>
@@ -11391,7 +11403,7 @@
         <v>0</v>
       </c>
       <c r="AR140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS140" s="1">
         <v>0</v>
@@ -11400,7 +11412,7 @@
         <v>0</v>
       </c>
       <c r="AU140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV140" s="1">
         <v>0</v>
@@ -11409,7 +11421,7 @@
         <v>0</v>
       </c>
       <c r="AX140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY140" s="1">
         <v>0</v>
@@ -11418,7 +11430,7 @@
         <v>0</v>
       </c>
       <c r="BA140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB140" s="1">
         <v>0</v>
@@ -11427,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="BD140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE140" s="1">
         <v>0</v>
@@ -11436,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="BG140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH140" s="1">
         <v>0</v>
@@ -11445,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="BJ140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK140" s="1">
         <v>0</v>
@@ -11454,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="BM140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN140" s="1">
         <v>0</v>
@@ -11472,7 +11484,7 @@
         <v>0</v>
       </c>
       <c r="CF140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CG140" s="1">
         <v>0</v>
@@ -11481,7 +11493,7 @@
         <v>0</v>
       </c>
       <c r="CI140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ140" s="1">
         <v>0</v>
@@ -11490,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="CL140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CM140" s="1">
         <v>0</v>
@@ -11499,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="CO140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CP140" s="1">
         <v>0</v>
@@ -11542,19 +11554,19 @@
         <v>0</v>
       </c>
       <c r="U142" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV142" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CP142" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV142" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF142" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET142" s="1">
         <v>0</v>
@@ -11611,19 +11623,19 @@
         <v>0</v>
       </c>
       <c r="U145" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV145" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CP145" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV145" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF145" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="ET145" s="1">
         <v>0</v>
@@ -11680,19 +11692,19 @@
         <v>0</v>
       </c>
       <c r="U148" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BV148" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CP148" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="DV148" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EF148" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="EQ148" s="1">
         <v>0</v>
